--- a/Team-Data/2013-14/1-15-2013-14.xlsx
+++ b/Team-Data/2013-14/1-15-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,25 +806,25 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -769,10 +836,10 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
@@ -787,7 +854,7 @@
         <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -802,13 +869,13 @@
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L3" t="n">
         <v>6.3</v>
@@ -873,31 +940,31 @@
         <v>18.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="P3" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W3" t="n">
         <v>6.8</v>
@@ -912,19 +979,19 @@
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
@@ -936,61 +1003,61 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW3" t="n">
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1112,19 +1179,19 @@
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1133,10 +1200,10 @@
         <v>19</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
         <v>4</v>
@@ -1151,7 +1218,7 @@
         <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
         <v>25</v>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1169,13 +1236,13 @@
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,19 +1292,19 @@
         <v>34.9</v>
       </c>
       <c r="J5" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="L5" t="n">
         <v>5.3</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O5" t="n">
         <v>18.3</v>
@@ -1246,7 +1313,7 @@
         <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
         <v>9.699999999999999</v>
@@ -1258,19 +1325,19 @@
         <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V5" t="n">
         <v>12.8</v>
       </c>
       <c r="W5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X5" t="n">
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
         <v>18.8</v>
@@ -1291,10 +1358,10 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
@@ -1315,7 +1382,7 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
         <v>11</v>
@@ -1324,10 +1391,10 @@
         <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1342,7 +1409,7 @@
         <v>2</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
@@ -1351,7 +1418,7 @@
         <v>25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -1389,97 +1456,97 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
         <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0.486</v>
+        <v>0.472</v>
       </c>
       <c r="H6" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="J6" t="n">
-        <v>80.7</v>
+        <v>79.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.423</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="M6" t="n">
-        <v>16.8</v>
+        <v>16.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.334</v>
+        <v>0.332</v>
       </c>
       <c r="O6" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
         <v>23.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R6" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T6" t="n">
-        <v>45.2</v>
+        <v>44.8</v>
       </c>
       <c r="U6" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="V6" t="n">
         <v>16.1</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X6" t="n">
         <v>5.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.3</v>
+        <v>91.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1500,25 +1567,25 @@
         <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV6" t="n">
         <v>27</v>
@@ -1536,10 +1603,10 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="H7" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L7" t="n">
         <v>7.3</v>
@@ -1601,19 +1668,19 @@
         <v>19.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O7" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="P7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R7" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
         <v>32.4</v>
@@ -1622,31 +1689,31 @@
         <v>44.4</v>
       </c>
       <c r="U7" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V7" t="n">
         <v>15.1</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB7" t="n">
         <v>96.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.7</v>
+        <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
         <v>8</v>
@@ -1658,7 +1725,7 @@
         <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
@@ -1667,7 +1734,7 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>28</v>
@@ -1676,13 +1743,13 @@
         <v>17</v>
       </c>
       <c r="AM7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>20</v>
@@ -1700,28 +1767,28 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ7" t="n">
         <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
         <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.575</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="J8" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.468</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.381</v>
+        <v>0.378</v>
       </c>
       <c r="O8" t="n">
         <v>16</v>
@@ -1792,43 +1859,43 @@
         <v>20</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.801</v>
       </c>
       <c r="R8" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>30.2</v>
       </c>
       <c r="T8" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA8" t="n">
         <v>18.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.7</v>
+        <v>103.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,19 +1904,19 @@
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1858,13 +1925,13 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1873,19 +1940,19 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>26</v>
       </c>
       <c r="AT8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1900,10 +1967,10 @@
         <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -1935,52 +2002,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.526</v>
+        <v>0.514</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="J9" t="n">
         <v>84.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q9" t="n">
         <v>0.729</v>
       </c>
       <c r="R9" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T9" t="n">
         <v>46.2</v>
@@ -1989,7 +2056,7 @@
         <v>22.1</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
@@ -1998,37 +2065,37 @@
         <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA9" t="n">
         <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.2</v>
+        <v>102.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE9" t="n">
         <v>12</v>
       </c>
-      <c r="AE9" t="n">
-        <v>11</v>
-      </c>
       <c r="AF9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
@@ -2037,13 +2104,13 @@
         <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2052,7 +2119,7 @@
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2067,7 +2134,7 @@
         <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
@@ -2076,10 +2143,10 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>18</v>
@@ -2207,16 +2274,16 @@
         <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>27</v>
@@ -2249,7 +2316,7 @@
         <v>18</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2258,10 +2325,10 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
         <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.625</v>
+        <v>0.641</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,7 +2384,7 @@
         <v>39.1</v>
       </c>
       <c r="J11" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="K11" t="n">
         <v>0.463</v>
@@ -2326,34 +2393,34 @@
         <v>9.4</v>
       </c>
       <c r="M11" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="P11" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.734</v>
+        <v>0.728</v>
       </c>
       <c r="R11" t="n">
         <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="T11" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="U11" t="n">
         <v>23.2</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W11" t="n">
         <v>7.8</v>
@@ -2362,31 +2429,31 @@
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.6</v>
+        <v>103.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2395,7 +2462,7 @@
         <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>7</v>
@@ -2407,19 +2474,19 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2440,16 +2507,16 @@
         <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA11" t="n">
         <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.65</v>
+        <v>0.641</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,61 +2566,61 @@
         <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O12" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="P12" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T12" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.4</v>
       </c>
       <c r="X12" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.2</v>
+        <v>105.3</v>
       </c>
       <c r="AC12" t="n">
         <v>3.6</v>
@@ -2601,13 +2668,13 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>24</v>
@@ -2616,7 +2683,7 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,13 +2692,13 @@
         <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2756,22 +2823,22 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
       </c>
       <c r="AM13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2795,10 +2862,10 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -2807,10 +2874,10 @@
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.675</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J14" t="n">
         <v>82.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="M14" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.339</v>
+        <v>0.333</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R14" t="n">
         <v>10.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T14" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U14" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
@@ -2911,22 +2978,22 @@
         <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.9</v>
+        <v>105.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2938,22 +3005,22 @@
         <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2968,10 +3035,10 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2980,10 +3047,10 @@
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J15" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P15" t="n">
         <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.751</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
         <v>43</v>
       </c>
       <c r="U15" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V15" t="n">
         <v>15.5</v>
@@ -3087,19 +3154,19 @@
         <v>6.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>20.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.2</v>
+        <v>99.8</v>
       </c>
       <c r="AC15" t="n">
         <v>-5.7</v>
@@ -3114,7 +3181,7 @@
         <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3126,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
         <v>15</v>
@@ -3144,7 +3211,7 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,28 +3220,28 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -3209,49 +3276,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.486</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
         <v>83.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
         <v>21.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="R16" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S16" t="n">
         <v>31</v>
@@ -3260,37 +3327,37 @@
         <v>43.2</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
         <v>5.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA16" t="n">
         <v>19.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -3302,7 +3369,7 @@
         <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
         <v>14</v>
@@ -3317,28 +3384,28 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
       </c>
       <c r="AT16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU16" t="n">
         <v>14</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3347,19 +3414,19 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA16" t="n">
         <v>22</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA16" t="n">
+      <c r="BB16" t="n">
         <v>21</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -3391,70 +3458,70 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
         <v>27</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.711</v>
+        <v>0.73</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J17" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.507</v>
+        <v>0.509</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
         <v>21.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O17" t="n">
         <v>18.2</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T17" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z17" t="n">
         <v>19.7</v>
@@ -3463,25 +3530,25 @@
         <v>21.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.1</v>
+        <v>104.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="n">
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
         <v>6</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3544,7 +3611,7 @@
         <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -3573,55 +3640,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.184</v>
+        <v>0.189</v>
       </c>
       <c r="H18" t="n">
         <v>48.9</v>
       </c>
       <c r="I18" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J18" t="n">
         <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.419</v>
+        <v>0.42</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
         <v>20.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="P18" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.766</v>
       </c>
       <c r="R18" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S18" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T18" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>20.5</v>
@@ -3630,28 +3697,28 @@
         <v>15.8</v>
       </c>
       <c r="W18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X18" t="n">
         <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.3</v>
+        <v>91.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,13 +3730,13 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3678,10 +3745,10 @@
         <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,22 +3757,22 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>24</v>
@@ -3720,10 +3787,10 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.474</v>
+        <v>0.486</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3773,7 +3840,7 @@
         <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.434</v>
@@ -3782,10 +3849,10 @@
         <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O19" t="n">
         <v>21.4</v>
@@ -3794,16 +3861,16 @@
         <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R19" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="S19" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T19" t="n">
-        <v>45.8</v>
+        <v>46.1</v>
       </c>
       <c r="U19" t="n">
         <v>23.5</v>
@@ -3812,7 +3879,7 @@
         <v>14.1</v>
       </c>
       <c r="W19" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>3.2</v>
@@ -3821,28 +3888,28 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>107.1</v>
+        <v>107</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -3857,13 +3924,13 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AM19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO19" t="n">
         <v>2</v>
@@ -3884,7 +3951,7 @@
         <v>5</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
         <v>8</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -3937,46 +4004,46 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.395</v>
+        <v>0.405</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>85.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M20" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N20" t="n">
         <v>0.386</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R20" t="n">
         <v>12.8</v>
@@ -3988,7 +4055,7 @@
         <v>43.2</v>
       </c>
       <c r="U20" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V20" t="n">
         <v>13.7</v>
@@ -4000,61 +4067,61 @@
         <v>6.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
       </c>
       <c r="AF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG20" t="n">
         <v>20</v>
       </c>
-      <c r="AG20" t="n">
-        <v>21</v>
-      </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM20" t="n">
         <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
         <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
@@ -4063,7 +4130,7 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>12</v>
@@ -4078,13 +4145,13 @@
         <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -4197,28 +4264,28 @@
         <v>-2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>8</v>
@@ -4227,7 +4294,7 @@
         <v>8</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>20</v>
@@ -4263,13 +4330,13 @@
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>4</v>
@@ -4391,13 +4458,13 @@
         <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4409,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4433,10 +4500,10 @@
         <v>16</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4445,13 +4512,13 @@
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -4483,82 +4550,82 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.256</v>
+        <v>0.263</v>
       </c>
       <c r="H23" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="I23" t="n">
-        <v>36.5</v>
+        <v>36.1</v>
       </c>
       <c r="J23" t="n">
-        <v>82.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L23" t="n">
         <v>7.3</v>
       </c>
       <c r="M23" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="O23" t="n">
         <v>15.8</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R23" t="n">
         <v>9.5</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-6.1</v>
       </c>
       <c r="AD23" t="n">
         <v>8</v>
@@ -4573,16 +4640,16 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
         <v>18</v>
@@ -4591,49 +4658,49 @@
         <v>15</v>
       </c>
       <c r="AN23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP23" t="n">
         <v>24</v>
       </c>
-      <c r="AO23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>26</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
       </c>
       <c r="AX23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY23" t="n">
         <v>27</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
         <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>0.342</v>
+        <v>0.324</v>
       </c>
       <c r="H24" t="n">
         <v>48.9</v>
@@ -4683,46 +4750,46 @@
         <v>39.4</v>
       </c>
       <c r="J24" t="n">
-        <v>88.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
         <v>7.2</v>
       </c>
       <c r="M24" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="O24" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P24" t="n">
         <v>22.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.713</v>
+        <v>0.717</v>
       </c>
       <c r="R24" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="T24" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U24" t="n">
         <v>22.9</v>
       </c>
       <c r="V24" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W24" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X24" t="n">
         <v>4.4</v>
@@ -4737,64 +4804,64 @@
         <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>102.3</v>
+        <v>102.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.1</v>
+        <v>-8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
         <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>19</v>
       </c>
       <c r="AM24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AN24" t="n">
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
         <v>8</v>
       </c>
       <c r="AT24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU24" t="n">
         <v>9</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>0.579</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="J25" t="n">
-        <v>84.7</v>
+        <v>84.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O25" t="n">
         <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q25" t="n">
         <v>0.75</v>
       </c>
       <c r="R25" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W25" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X25" t="n">
         <v>5.2</v>
@@ -4916,16 +4983,16 @@
         <v>21.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,7 +5001,7 @@
         <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
@@ -4943,7 +5010,7 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK25" t="n">
         <v>13</v>
@@ -4955,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
@@ -4967,22 +5034,22 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
         <v>17</v>
       </c>
       <c r="AT25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU25" t="n">
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.763</v>
+        <v>0.757</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J26" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
         <v>10.3</v>
@@ -5059,55 +5126,55 @@
         <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="O26" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.821</v>
       </c>
       <c r="R26" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T26" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V26" t="n">
         <v>13.9</v>
       </c>
       <c r="W26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB26" t="n">
         <v>109.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5140,10 +5207,10 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5161,19 +5228,19 @@
         <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.378</v>
+        <v>0.361</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J27" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.451</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>6.9</v>
       </c>
       <c r="M27" t="n">
+        <v>20</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="O27" t="n">
         <v>19.8</v>
       </c>
-      <c r="N27" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="O27" t="n">
-        <v>19.6</v>
-      </c>
       <c r="P27" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R27" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U27" t="n">
         <v>20.2</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="W27" t="n">
         <v>7.9</v>
@@ -5274,7 +5341,7 @@
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z27" t="n">
         <v>22.8</v>
@@ -5283,28 +5350,28 @@
         <v>22.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>102</v>
+        <v>101.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE27" t="n">
         <v>25</v>
       </c>
-      <c r="AE27" t="n">
-        <v>23</v>
-      </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
@@ -5316,13 +5383,13 @@
         <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
         <v>7</v>
@@ -5331,22 +5398,22 @@
         <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
         <v>18</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.795</v>
+        <v>0.789</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.493</v>
+        <v>0.491</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.399</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
         <v>14.8</v>
@@ -5432,31 +5499,31 @@
         <v>19.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R28" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X28" t="n">
         <v>4.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
         <v>17.5</v>
@@ -5465,10 +5532,10 @@
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>8</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5498,7 +5565,7 @@
         <v>9</v>
       </c>
       <c r="AM28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5510,16 +5577,16 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS28" t="n">
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5531,10 +5598,10 @@
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5543,7 +5610,7 @@
         <v>27</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -5575,49 +5642,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
         <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.514</v>
+        <v>0.528</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>35.7</v>
+        <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M29" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O29" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P29" t="n">
         <v>25.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.772</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S29" t="n">
         <v>31.1</v>
@@ -5626,46 +5693,46 @@
         <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V29" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" t="n">
         <v>22.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
         <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI29" t="n">
         <v>26</v>
@@ -5677,13 +5744,13 @@
         <v>25</v>
       </c>
       <c r="AL29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM29" t="n">
         <v>13</v>
       </c>
-      <c r="AM29" t="n">
-        <v>12</v>
-      </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
@@ -5692,7 +5759,7 @@
         <v>8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>9</v>
@@ -5701,7 +5768,7 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>26</v>
@@ -5710,16 +5777,16 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -5757,67 +5824,67 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" t="n">
         <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.325</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L30" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O30" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
         <v>21.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="R30" t="n">
         <v>11.2</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U30" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
         <v>5.1</v>
@@ -5829,22 +5896,22 @@
         <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF30" t="n">
         <v>27</v>
       </c>
-      <c r="AF30" t="n">
-        <v>28</v>
-      </c>
       <c r="AG30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5856,7 +5923,7 @@
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5868,10 +5935,10 @@
         <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
@@ -5880,25 +5947,25 @@
         <v>14</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>21</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
         <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>0.486</v>
+        <v>0.472</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J31" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
         <v>7.9</v>
@@ -5969,28 +6036,28 @@
         <v>20.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.732</v>
+        <v>0.729</v>
       </c>
       <c r="R31" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S31" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U31" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V31" t="n">
         <v>15.1</v>
@@ -5999,46 +6066,46 @@
         <v>8.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
         <v>20.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF31" t="n">
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI31" t="n">
         <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6053,25 +6120,25 @@
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AS31" t="n">
         <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
@@ -6083,10 +6150,10 @@
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-15-2013-14</t>
+          <t>2014-01-15</t>
         </is>
       </c>
     </row>
